--- a/GWD Data/ZCost Index.xlsx
+++ b/GWD Data/ZCost Index.xlsx
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A97D103-B55E-42ED-91D3-7AA121F7B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FF0967-F424-4A1E-8908-CBB8B58CB9A6}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/ZCost Index.xlsx
+++ b/GWD Data/ZCost Index.xlsx
@@ -269,7 +269,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_13" displayName="Table_13" ref="A1:B16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_12" displayName="Table_12" ref="A1:B16">
   <tableColumns count="2">
     <tableColumn id="1" name="District"/>
     <tableColumn id="2" name="Index"/>
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FF0967-F424-4A1E-8908-CBB8B58CB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B0B40C0-5BF3-4EDC-A852-7F0224FCB9A6}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
